--- a/SNAP.xlsx
+++ b/SNAP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20446BF7-6966-4ECA-88DB-A6E854203893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AACBEB9-8290-4CF8-8A99-4D3C43F45989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{AE35FE02-C0F4-427E-A3D8-609427A1DAE9}"/>
+    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" xr2:uid="{AE35FE02-C0F4-427E-A3D8-609427A1DAE9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -718,7 +718,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>8.2100000000000009</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -742,7 +742,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>14115.934196310003</v>
+        <v>9886.3120132500007</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -778,7 +778,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>14660.446196310004</v>
+        <v>10430.82401325</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">

--- a/SNAP.xlsx
+++ b/SNAP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AACBEB9-8290-4CF8-8A99-4D3C43F45989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CA3DA0-3F83-4F7D-876D-163BA3850B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" xr2:uid="{AE35FE02-C0F4-427E-A3D8-609427A1DAE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AE35FE02-C0F4-427E-A3D8-609427A1DAE9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -718,7 +718,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="2">
-        <v>5.75</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -742,7 +742,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>9886.3120132500007</v>
+        <v>7599.5650606200006</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -778,7 +778,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>10430.82401325</v>
+        <v>8144.0770606200012</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
